--- a/Result/profitability/3703.xlsx
+++ b/Result/profitability/3703.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM65"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4</v>
+        <v>0.345</v>
       </c>
       <c r="N2" t="n">
-        <v>12.33875</v>
+        <v>12.5925</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.38</v>
+        <v>0.43125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.41</v>
+        <v>12.8375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>99.3</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.40375</v>
+        <v>0.4275</v>
       </c>
       <c r="N4" t="n">
-        <v>12.80125</v>
+        <v>13.32875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -8685,6 +8685,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3703</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7425</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6358</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F66" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="G66" t="n">
+        <v>421</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>-60</v>
+      </c>
+      <c r="J66" t="n">
+        <v>361</v>
+      </c>
+      <c r="K66" t="n">
+        <v>201</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="N66" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-0.09000000000000002</v>
+      </c>
+      <c r="X66" t="n">
+        <v>-0.2727272727272728</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>-0.01000000000000156</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-0.0006954102920724292</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-0.3142857142857143</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.3884057971014492</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
